--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,130 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104760137</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98197</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Baklidhöjden 1, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>619908</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6963778</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Y-Här-0051</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-08-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-08-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>104760137</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>104760137</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,11 +819,6 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>104760137</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,6 +819,11 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>104760137</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>104760137</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>104760137</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>104760137</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>104760137</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>104760137</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51565-2022 artfynd.xlsx
+++ b/artfynd/A 51565-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,130 +799,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>104760137</v>
-      </c>
-      <c r="B3" t="n">
-        <v>98355</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Baklidhöjden 1, Ång</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>619908</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6963778</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Härnösand</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Viksjö</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Y-Här-0051</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
